--- a/app/data/orders.xlsx
+++ b/app/data/orders.xlsx
@@ -445,13 +445,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -459,6 +459,15 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -517,6 +526,51 @@
           <t>button_style</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>order_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>delivery_date</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>delivery_time</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>delivered_by</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>delivery_status</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>advance</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>remaining</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -536,7 +590,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -550,6 +604,15 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/data/orders.xlsx
+++ b/app/data/orders.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Section" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data Section" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +449,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>owais</t>
+          <t>C-101</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
